--- a/data-manipulation-scripts/sheets-cleanup/sheets/COXIM APOIO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/COXIM APOIO.xlsx
@@ -31,7 +31,7 @@
     <t>5637300001</t>
   </si>
   <si>
-    <t xml:space="preserve">COXIM APOIO TANQUE  WR XTREME CG150 </t>
+    <t xml:space="preserve">COXIM APOIO TANQUE  EXTREMO CG150 </t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -92,7 +92,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -362,7 +362,9 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="4">
+        <v>1.0</v>
+      </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
